--- a/6.1 Myrmidon disturbance/output/Rugosity_growth_param_0.5.xlsx
+++ b/6.1 Myrmidon disturbance/output/Rugosity_growth_param_0.5.xlsx
@@ -448,7 +448,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.560685206409081</v>
+        <v>1.598713257699176</v>
       </c>
     </row>
     <row r="4">
@@ -456,7 +456,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.038276112408743</v>
+        <v>1.065178840444139</v>
       </c>
     </row>
     <row r="5">
@@ -464,7 +464,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.055727316478611</v>
+        <v>1.095202823663751</v>
       </c>
     </row>
     <row r="6">
@@ -472,7 +472,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.095530138900798</v>
+        <v>1.148490949538291</v>
       </c>
     </row>
     <row r="7">
@@ -480,7 +480,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.14304847186114</v>
+        <v>1.208567737256518</v>
       </c>
     </row>
     <row r="8">
@@ -488,7 +488,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.214151668623562</v>
+        <v>1.292841266640148</v>
       </c>
     </row>
     <row r="9">
@@ -496,7 +496,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.308781572908432</v>
+        <v>1.40237962117813</v>
       </c>
     </row>
     <row r="10">
@@ -504,7 +504,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.473798283329331</v>
+        <v>1.583359419428278</v>
       </c>
     </row>
     <row r="11">
@@ -512,7 +512,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.667097657761809</v>
+        <v>1.785497586309806</v>
       </c>
     </row>
     <row r="12">
@@ -520,7 +520,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.880485349515063</v>
+        <v>2.002431904121768</v>
       </c>
     </row>
     <row r="13">
@@ -528,7 +528,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.115432984653291</v>
+        <v>2.241507989426281</v>
       </c>
     </row>
     <row r="14">
@@ -536,7 +536,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.331388611296346</v>
+        <v>2.455023024699491</v>
       </c>
     </row>
     <row r="15">
@@ -544,7 +544,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2.530306747751714</v>
+        <v>2.653612405886108</v>
       </c>
     </row>
     <row r="16">
@@ -552,7 +552,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.684851390049114</v>
+        <v>2.808597369957244</v>
       </c>
     </row>
     <row r="17">
@@ -560,7 +560,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.860953553551898</v>
+        <v>1.978397390865193</v>
       </c>
     </row>
   </sheetData>
